--- a/data/trans_camb/P19C04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 5,68</t>
+          <t>-3,98; 6,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 0,71</t>
+          <t>-8,52; 0,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -0,55</t>
+          <t>-8,58; -0,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 8,54</t>
+          <t>-1,33; 8,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 5,08</t>
+          <t>-3,41; 5,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,92</t>
+          <t>-5,69; 0,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 5,42</t>
+          <t>-2,01; 5,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 1,15</t>
+          <t>-5,25; 1,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -0,78</t>
+          <t>-6,6; -0,96</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 54,95</t>
+          <t>-26,31; 62,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 6,59</t>
+          <t>-54,05; 7,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,53; -4,89</t>
+          <t>-55,94; -4,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 183,19</t>
+          <t>-14,92; 175,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 108,33</t>
+          <t>-37,55; 121,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,33; 19,98</t>
+          <t>-59,48; 19,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 61,27</t>
+          <t>-16,5; 59,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 13,73</t>
+          <t>-43,93; 12,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,97; -7,38</t>
+          <t>-53,32; -11,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 5,03</t>
+          <t>-6,97; 5,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 2,65</t>
+          <t>-8,94; 2,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; -0,35</t>
+          <t>-10,76; -0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 7,85</t>
+          <t>-1,66; 7,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 2,8</t>
+          <t>-5,71; 2,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 1,78</t>
+          <t>-5,86; 1,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,63</t>
+          <t>-2,08; 5,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,6</t>
+          <t>-5,78; 1,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -0,26</t>
+          <t>-6,55; -0,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 39,82</t>
+          <t>-37,42; 41,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,61; 23,13</t>
+          <t>-47,52; 24,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,59; -1,74</t>
+          <t>-56,28; -1,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 140,19</t>
+          <t>-16,72; 136,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 54,91</t>
+          <t>-59,68; 50,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,95; 37,2</t>
+          <t>-57,16; 31,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 61,67</t>
+          <t>-15,78; 55,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,06; 18,3</t>
+          <t>-43,37; 15,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -1,36</t>
+          <t>-47,67; -1,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 10,0</t>
+          <t>-0,95; 10,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 2,07</t>
+          <t>-8,52; 1,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,19; -4,6</t>
+          <t>-21,03; -4,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 3,7</t>
+          <t>-9,96; 4,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 11,24</t>
+          <t>-6,88; 10,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 3,7</t>
+          <t>-10,41; 3,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 6,7</t>
+          <t>-2,54; 6,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 3,01</t>
+          <t>-6,64; 2,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,58; -4,26</t>
+          <t>-17,71; -4,25</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 53,52</t>
+          <t>-3,79; 56,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 11,13</t>
+          <t>-35,82; 11,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,4; -22,41</t>
+          <t>-84,26; -20,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 42,59</t>
+          <t>-53,17; 48,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 114,35</t>
+          <t>-42,03; 107,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,4; 48,0</t>
+          <t>-56,32; 47,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 39,71</t>
+          <t>-12,11; 40,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 18,5</t>
+          <t>-29,34; 17,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,79; -23,97</t>
+          <t>-80,49; -22,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 11,68</t>
+          <t>2,86; 11,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 0,24</t>
+          <t>-8,51; -0,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,01; -3,14</t>
+          <t>-10,97; -3,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,7</t>
+          <t>-4,44; 4,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,43</t>
+          <t>-7,28; 0,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,75; -3,77</t>
+          <t>-14,13; -3,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,2</t>
+          <t>0,49; 6,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,01; -1,28</t>
+          <t>-7,16; -1,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -5,35</t>
+          <t>-12,96; -5,37</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,66; 50,42</t>
+          <t>10,48; 48,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 1,06</t>
+          <t>-30,93; -1,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,4; -13,52</t>
+          <t>-39,84; -14,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 27,04</t>
+          <t>-24,81; 31,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 3,63</t>
+          <t>-40,67; 5,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,34; -26,67</t>
+          <t>-76,01; -26,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 35,58</t>
+          <t>2,23; 34,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,85; -6,18</t>
+          <t>-30,71; -6,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,23; -26,49</t>
+          <t>-58,16; -26,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,45</t>
+          <t>2,02; 16,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 10,14</t>
+          <t>-4,33; 10,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 9,29</t>
+          <t>-4,12; 9,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,71</t>
+          <t>-1,28; 9,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 0,54</t>
+          <t>-9,53; 0,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 0,38</t>
+          <t>-9,34; 0,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 10,49</t>
+          <t>1,95; 10,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 3,43</t>
+          <t>-4,71; 3,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 2,03</t>
+          <t>-6,17; 2,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6,35; 79,79</t>
+          <t>7,21; 84,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 51,58</t>
+          <t>-14,67; 50,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 46,25</t>
+          <t>-14,66; 45,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 52,25</t>
+          <t>-5,54; 51,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 4,27</t>
+          <t>-41,91; 1,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 1,9</t>
+          <t>-42,82; 2,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,52; 55,31</t>
+          <t>7,92; 52,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 17,41</t>
+          <t>-20,37; 16,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 9,82</t>
+          <t>-25,69; 11,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 5,4</t>
+          <t>-5,93; 5,25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 5,26</t>
+          <t>-5,98; 5,24</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 4,7</t>
+          <t>-8,66; 4,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,63; 8,07</t>
+          <t>1,18; 8,46</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,8</t>
+          <t>-3,13; 3,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 0,2</t>
+          <t>-6,18; 0,01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,78</t>
+          <t>0,76; 6,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,7</t>
+          <t>-3,29; 2,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,3; -0,3</t>
+          <t>-6,08; -0,27</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 81,45</t>
+          <t>-46,37; 78,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 83,79</t>
+          <t>-47,04; 80,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 80,16</t>
+          <t>-73,09; 62,52</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,75; 56,04</t>
+          <t>6,48; 58,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 26,19</t>
+          <t>-18,1; 25,08</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 0,86</t>
+          <t>-34,4; -0,35</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,13; 49,51</t>
+          <t>4,71; 51,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 19,48</t>
+          <t>-19,6; 21,19</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-37,88; -2,31</t>
+          <t>-36,88; -2,01</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,19</t>
+          <t>2,49; 7,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,26</t>
+          <t>-4,34; 0,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,57; -3,48</t>
+          <t>-9,2; -3,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,06</t>
+          <t>0,97; 4,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,18</t>
+          <t>-3,38; 0,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,62; -2,52</t>
+          <t>-6,62; -2,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,42</t>
+          <t>2,32; 5,29</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,26</t>
+          <t>-3,24; -0,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -3,24</t>
+          <t>-6,65; -3,22</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,39; 38,68</t>
+          <t>11,94; 38,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 1,08</t>
+          <t>-20,13; 1,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,31; -18,39</t>
+          <t>-45,14; -17,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5,47; 36,64</t>
+          <t>5,97; 33,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 1,29</t>
+          <t>-21,72; 2,33</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,52; -18,26</t>
+          <t>-42,83; -18,13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,22; 33,22</t>
+          <t>13,0; 32,52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -1,84</t>
+          <t>-18,09; -1,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-37,25; -19,53</t>
+          <t>-37,42; -19,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-4,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>-2,37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-3,82</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 6,51</t>
+          <t>-4,31; 6,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 0,55</t>
+          <t>-8,69; 1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -0,48</t>
+          <t>-8,57; -0,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 8,41</t>
+          <t>-0,91; 9,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 5,26</t>
+          <t>-3,87; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,77</t>
+          <t>-6,68; 0,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 5,3</t>
+          <t>-1,67; 5,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 1,01</t>
+          <t>-5,52; 1,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; -0,96</t>
+          <t>-6,92; -1,1</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-34,6%</t>
+          <t>-34,43%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-32,7%</t>
+          <t>-33,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-36,16%</t>
+          <t>-36,43%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 62,59</t>
+          <t>-27,8; 56,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 7,59</t>
+          <t>-56,31; 10,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,94; -4,66</t>
+          <t>-56,29; -0,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 175,36</t>
+          <t>-10,37; 193,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,55; 121,67</t>
+          <t>-42,1; 108,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,48; 19,33</t>
+          <t>-62,65; 16,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 59,01</t>
+          <t>-14,0; 64,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,93; 12,28</t>
+          <t>-45,22; 14,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,32; -11,15</t>
+          <t>-54,19; -12,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,23</t>
+          <t>-5,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-3,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 5,04</t>
+          <t>-6,37; 4,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 2,87</t>
+          <t>-8,75; 2,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -0,26</t>
+          <t>-10,65; -0,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 7,68</t>
+          <t>-1,64; 7,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 2,54</t>
+          <t>-5,76; 2,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,49</t>
+          <t>-5,51; 1,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,37</t>
+          <t>-2,48; 5,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 1,4</t>
+          <t>-5,61; 1,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -0,13</t>
+          <t>-6,16; 0,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-33,88%</t>
+          <t>-34,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-24,07%</t>
+          <t>-23,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-27,7%</t>
+          <t>-28,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 41,28</t>
+          <t>-34,82; 39,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 24,73</t>
+          <t>-47,74; 21,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,28; -1,15</t>
+          <t>-56,1; -1,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 136,44</t>
+          <t>-18,31; 149,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 50,44</t>
+          <t>-56,45; 58,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 31,3</t>
+          <t>-53,46; 31,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 55,23</t>
+          <t>-18,81; 53,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 15,48</t>
+          <t>-42,82; 16,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,67; -1,09</t>
+          <t>-46,65; 0,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-11,85</t>
+          <t>-5,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,24</t>
+          <t>-3,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-9,78</t>
+          <t>-5,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 10,29</t>
+          <t>-0,76; 10,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 1,94</t>
+          <t>-8,62; 1,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,03; -4,36</t>
+          <t>-10,53; -0,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 4,19</t>
+          <t>-9,36; 3,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 10,66</t>
+          <t>-7,12; 10,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 3,75</t>
+          <t>-10,89; 2,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,74</t>
+          <t>-2,33; 6,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 2,68</t>
+          <t>-7,2; 2,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -4,25</t>
+          <t>-9,43; -1,25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-55,55%</t>
+          <t>-26,29%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-23,69%</t>
+          <t>-23,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-50,27%</t>
+          <t>-26,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 56,67</t>
+          <t>-3,25; 54,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 11,05</t>
+          <t>-35,69; 10,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,26; -20,84</t>
+          <t>-45,26; -1,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 48,65</t>
+          <t>-54,25; 40,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,03; 107,03</t>
+          <t>-42,36; 109,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,32; 47,47</t>
+          <t>-57,87; 29,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 40,47</t>
+          <t>-11,82; 38,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 17,61</t>
+          <t>-32,31; 13,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-80,49; -22,34</t>
+          <t>-42,97; -6,74</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,96</t>
+          <t>-6,31</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,57</t>
+          <t>-5,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,04</t>
+          <t>-6,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,49</t>
+          <t>3,15; 11,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -0,37</t>
+          <t>-8,05; -0,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -3,6</t>
+          <t>-10,27; -2,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 4,22</t>
+          <t>-4,5; 3,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 0,74</t>
+          <t>-7,28; 0,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -3,64</t>
+          <t>-8,58; -1,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,82</t>
+          <t>0,75; 7,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -1,35</t>
+          <t>-7,13; -1,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,96; -5,37</t>
+          <t>-8,78; -3,37</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-27,6%</t>
+          <t>-25,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-47,43%</t>
+          <t>-31,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-37,44%</t>
+          <t>-28,05%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,48; 48,37</t>
+          <t>11,38; 49,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,93; -1,53</t>
+          <t>-28,99; -1,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,84; -14,95</t>
+          <t>-37,35; -10,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 31,75</t>
+          <t>-25,0; 27,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 5,93</t>
+          <t>-40,53; 7,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,01; -26,06</t>
+          <t>-47,19; -11,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 34,18</t>
+          <t>3,3; 35,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,71; -6,78</t>
+          <t>-30,74; -6,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,16; -26,57</t>
+          <t>-37,5; -16,78</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>0,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 16,33</t>
+          <t>1,68; 15,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 10,14</t>
+          <t>-4,18; 9,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 9,04</t>
+          <t>-2,13; 11,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 9,03</t>
+          <t>-1,06; 9,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 0,29</t>
+          <t>-9,26; 1,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 0,49</t>
+          <t>-6,71; 2,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 10,07</t>
+          <t>1,63; 10,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 3,28</t>
+          <t>-4,94; 3,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 2,28</t>
+          <t>-2,84; 4,71</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-19,87%</t>
+          <t>-10,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-7,69%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,21; 84,85</t>
+          <t>5,26; 76,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 50,21</t>
+          <t>-14,2; 47,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 45,7</t>
+          <t>-7,76; 56,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 51,71</t>
+          <t>-4,45; 54,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 1,83</t>
+          <t>-40,74; 6,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 2,58</t>
+          <t>-28,61; 13,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,92; 52,38</t>
+          <t>6,69; 53,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 16,95</t>
+          <t>-20,53; 15,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 11,61</t>
+          <t>-12,15; 24,53</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-2,52</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,29</t>
+          <t>-3,23</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 5,25</t>
+          <t>-5,91; 5,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 5,24</t>
+          <t>-6,62; 4,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 4,11</t>
+          <t>-8,16; 5,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,18; 8,46</t>
+          <t>0,99; 8,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,67</t>
+          <t>-3,23; 3,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,01</t>
+          <t>-6,47; -0,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,74</t>
+          <t>0,5; 6,53</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,85</t>
+          <t>-3,13; 2,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -0,27</t>
+          <t>-5,93; -0,33</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-28,13%</t>
+          <t>-26,05%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-18,49%</t>
+          <t>-19,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-21,9%</t>
+          <t>-21,49%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 78,78</t>
+          <t>-46,05; 83,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-47,04; 80,83</t>
+          <t>-51,74; 62,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,09; 62,52</t>
+          <t>-70,86; 82,81</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,48; 58,89</t>
+          <t>5,16; 54,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 25,08</t>
+          <t>-18,23; 26,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,4; -0,35</t>
+          <t>-35,35; 0,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,71; 51,97</t>
+          <t>2,92; 49,22</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 21,19</t>
+          <t>-19,56; 20,49</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-36,88; -2,01</t>
+          <t>-35,89; -2,01</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-5,69</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-3,2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,85</t>
+          <t>-3,39</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,18</t>
+          <t>2,29; 6,89</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,27</t>
+          <t>-4,3; 0,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -3,26</t>
+          <t>-5,63; -1,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,68</t>
+          <t>0,92; 4,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,33</t>
+          <t>-3,47; 0,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,62; -2,36</t>
+          <t>-4,92; -1,68</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,29</t>
+          <t>2,3; 5,31</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,24</t>
+          <t>-3,27; -0,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -3,22</t>
+          <t>-4,7; -2,03</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-28,53%</t>
+          <t>-18,64%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-28,37%</t>
+          <t>-21,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-28,2%</t>
+          <t>-19,73%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>11,94; 38,13</t>
+          <t>10,76; 36,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 1,8</t>
+          <t>-20,3; 0,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-45,14; -17,87</t>
+          <t>-27,16; -9,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5,97; 33,65</t>
+          <t>5,6; 34,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 2,33</t>
+          <t>-22,6; 3,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,83; -18,13</t>
+          <t>-30,8; -12,09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,0; 32,52</t>
+          <t>12,95; 32,46</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -1,44</t>
+          <t>-18,03; -1,97</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-37,42; -19,63</t>
+          <t>-25,95; -11,94</t>
         </is>
       </c>
     </row>
